--- a/sections/04-what-vba-can-do/02-sheet-operations/book/sales.xlsx
+++ b/sections/04-what-vba-can-do/02-sheet-operations/book/sales.xlsx
@@ -1289,6 +1289,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rIdButtons"/>
 </worksheet>
 </file>